--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_40.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_40.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2385099.418162327</v>
+        <v>2378079.555308218</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9689683.050949618</v>
+        <v>9689683.050949613</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9689683.050949618</v>
+        <v>9689683.050949613</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138317.967070703</v>
+        <v>138317.9670706801</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138317.967070703</v>
+        <v>138317.9670706801</v>
       </c>
     </row>
     <row r="11">
@@ -672,10 +672,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>176.4246500889419</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>18.33383170272989</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -745,13 +745,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>199.8180013219742</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>178.6331552561881</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
@@ -894,7 +894,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>67.80840994572374</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>18.33383170272989</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -1021,16 +1021,16 @@
         <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>66.5639999646113</v>
+        <v>421</v>
       </c>
       <c r="T6" t="n">
-        <v>5.357765217513816</v>
+        <v>335.5681244750683</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>356.4849292625508</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1146,10 +1146,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>26.34349040625725</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>279.7324240682209</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1219,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>118.0893820455459</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>405.3577652175138</v>
+        <v>137.3438537259093</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1371,7 +1371,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D11" t="n">
-        <v>64.30454712526431</v>
+        <v>60.33915573984979</v>
       </c>
       <c r="E11" t="n">
         <v>54.36328960686865</v>
@@ -1380,7 +1380,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H11" t="n">
         <v>58.00965870352741</v>
@@ -1456,16 +1456,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>197.2737972923793</v>
@@ -1507,7 +1507,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>104.8452544534428</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X12" t="n">
         <v>69.86273944538755</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T14" t="n">
         <v>236.6755817285639</v>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S15" t="n">
         <v>116.5639999646113</v>
@@ -1750,7 +1750,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>244.9427694002283</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T17" t="n">
         <v>236.6755817285639</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1966,13 +1966,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T18" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U18" t="n">
         <v>50.21035976018675</v>
@@ -2167,16 +2167,16 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>73.04152018756567</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>197.2737972923793</v>
@@ -2218,7 +2218,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>104.8452544534428</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
         <v>69.86273944538755</v>
@@ -2316,7 +2316,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>103.4399696284084</v>
+        <v>99.47457824299391</v>
       </c>
       <c r="D23" t="n">
         <v>60.33915573984979</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T23" t="n">
         <v>236.6755817285639</v>
@@ -2404,10 +2404,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2446,10 +2446,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U24" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V24" t="n">
         <v>64.51066719152016</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>176.8481678023229</v>
+        <v>171.3439591877372</v>
       </c>
       <c r="T26" t="n">
         <v>268.6755817285639</v>
@@ -2619,7 +2619,7 @@
         <v>274.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>187.8132240682209</v>
+        <v>193.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2738,16 +2738,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>105.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>253.1850752716849</v>
+        <v>178.0058334593688</v>
       </c>
       <c r="O28" t="n">
-        <v>183.5017783082005</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>369.4478973282775</v>
@@ -2756,10 +2756,10 @@
         <v>407.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>408.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>44.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>86.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>85.75737228701621</v>
+        <v>80.25316367254632</v>
       </c>
       <c r="H29" t="n">
         <v>90.00965870352741</v>
@@ -2844,7 +2844,7 @@
         <v>268.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>325.7170879340252</v>
+        <v>331.2212965486107</v>
       </c>
       <c r="V29" t="n">
         <v>311.8510241668239</v>
@@ -2932,7 +2932,7 @@
         <v>114.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>101.8627394453875</v>
+        <v>101.8627394453614</v>
       </c>
       <c r="Y30" t="n">
         <v>81.39139276613435</v>
@@ -2978,22 +2978,22 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>253.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>322.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>344.8221193850964</v>
+        <v>369.4478973282775</v>
       </c>
       <c r="Q31" t="n">
         <v>407.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>408.6021279811511</v>
+        <v>10.97732208982004</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>92.33915573984979</v>
       </c>
       <c r="E32" t="n">
-        <v>80.85908099237</v>
+        <v>86.36328960686865</v>
       </c>
       <c r="F32" t="n">
         <v>86.88962870801186</v>
@@ -3042,7 +3042,7 @@
         <v>85.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>90.00965870352741</v>
+        <v>84.50545008902873</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>87.35776521751382</v>
       </c>
       <c r="U33" t="n">
-        <v>82.21035976018675</v>
+        <v>82.21035976016466</v>
       </c>
       <c r="V33" t="n">
         <v>96.51066719152016</v>
@@ -3215,7 +3215,7 @@
         <v>105.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N34" t="n">
         <v>253.1850752716849</v>
@@ -3227,7 +3227,7 @@
         <v>369.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>313.268960357639</v>
+        <v>110.6373489550891</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3403,10 +3403,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>155.4146630973942</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>69.86273944538755</v>
+        <v>132.54050197083</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3501,7 +3501,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>103.4399696284084</v>
+        <v>99.47457824299391</v>
       </c>
       <c r="D38" t="n">
         <v>60.33915573984979</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U39" t="n">
         <v>50.21035976018675</v>
@@ -3640,10 +3640,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>82.37314290982852</v>
+        <v>145.0509054352709</v>
       </c>
       <c r="X39" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
         <v>49.39139276613435</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3789,7 +3789,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>236.6755817285639</v>
+        <v>240.6409731139784</v>
       </c>
       <c r="U41" t="n">
         <v>299.2212965486107</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34.55655664632661</v>
+        <v>97.23431917176904</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3877,10 +3877,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>49.39139276613435</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T44" t="n">
         <v>236.6755817285639</v>
@@ -4051,19 +4051,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="F45" t="n">
-        <v>64.74007562773993</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>266.9273161322752</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>216.9529946747056</v>
+        <v>235.472016596655</v>
       </c>
       <c r="D2" t="n">
-        <v>206.5094030182917</v>
+        <v>225.028424940241</v>
       </c>
       <c r="E2" t="n">
-        <v>202.1020397790304</v>
+        <v>220.6210617009798</v>
       </c>
       <c r="F2" t="n">
-        <v>197.1630208820488</v>
+        <v>215.6820428039981</v>
       </c>
       <c r="G2" t="n">
-        <v>193.3676953396081</v>
+        <v>211.8867172615575</v>
       </c>
       <c r="H2" t="n">
-        <v>185.2771309926108</v>
+        <v>33.68</v>
       </c>
       <c r="I2" t="n">
         <v>33.68</v>
@@ -4324,10 +4324,10 @@
         <v>424.9891130376557</v>
       </c>
       <c r="K2" t="n">
-        <v>433.6300000000001</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="L2" t="n">
-        <v>433.6300000000001</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="M2" t="n">
         <v>433.6300000000001</v>
@@ -4336,7 +4336,7 @@
         <v>850.4200000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>850.4200000000001</v>
+        <v>1267.21</v>
       </c>
       <c r="P2" t="n">
         <v>1267.21</v>
@@ -4345,28 +4345,28 @@
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1665.480978078051</v>
+        <v>1684</v>
       </c>
       <c r="S2" t="n">
-        <v>1569.674747974694</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1381.113554309478</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>1129.374870927043</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>897.2021192433824</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>656.4208303737385</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>462.1967561710438</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>349.7549049762899</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>398.4273863086054</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="C3" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="D3" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="E3" t="n">
-        <v>33.68</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="F3" t="n">
-        <v>33.68</v>
+        <v>698.2331546075238</v>
       </c>
       <c r="G3" t="n">
-        <v>33.68</v>
+        <v>369.2033203903244</v>
       </c>
       <c r="H3" t="n">
         <v>33.68</v>
@@ -4427,25 +4427,25 @@
         <v>1040.351008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>859.9134784002856</v>
+        <v>973.1146453614743</v>
       </c>
       <c r="T3" t="n">
-        <v>854.5015943421909</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>854.2891097359416</v>
+        <v>967.4902766971303</v>
       </c>
       <c r="V3" t="n">
-        <v>839.6318701485475</v>
+        <v>952.8330371097362</v>
       </c>
       <c r="W3" t="n">
-        <v>806.9317257951853</v>
+        <v>920.1328927563741</v>
       </c>
       <c r="X3" t="n">
-        <v>786.8683526180262</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="Y3" t="n">
-        <v>786.8683526180262</v>
+        <v>900.0695195792149</v>
       </c>
     </row>
     <row r="4">
@@ -4455,19 +4455,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>561.9623182976904</v>
+        <v>590.8099231905247</v>
       </c>
       <c r="C4" t="n">
-        <v>687.9643241161262</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="D4" t="n">
-        <v>801.2834682411263</v>
+        <v>647.8769023542411</v>
       </c>
       <c r="E4" t="n">
-        <v>919.1123724525394</v>
+        <v>765.7058065656541</v>
       </c>
       <c r="F4" t="n">
-        <v>1043.473345044475</v>
+        <v>890.0667791575896</v>
       </c>
       <c r="G4" t="n">
         <v>1043.473345044475</v>
@@ -4512,19 +4512,19 @@
         <v>33.68</v>
       </c>
       <c r="U4" t="n">
-        <v>33.68</v>
+        <v>280.2311926382866</v>
       </c>
       <c r="V4" t="n">
-        <v>33.68</v>
+        <v>479.0525855242326</v>
       </c>
       <c r="W4" t="n">
-        <v>205.5709182596774</v>
+        <v>479.0525855242326</v>
       </c>
       <c r="X4" t="n">
-        <v>338.7956799523661</v>
+        <v>479.0525855242326</v>
       </c>
       <c r="Y4" t="n">
-        <v>450.2049806313983</v>
+        <v>479.0525855242326</v>
       </c>
     </row>
     <row r="5">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266.9273161322752</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C5" t="n">
         <v>216.9529946747056</v>
@@ -4558,52 +4558,52 @@
         <v>33.68</v>
       </c>
       <c r="J5" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="K5" t="n">
-        <v>841.7791130376557</v>
+        <v>33.68</v>
       </c>
       <c r="L5" t="n">
-        <v>841.7791130376557</v>
+        <v>33.68</v>
       </c>
       <c r="M5" t="n">
-        <v>850.4200000000001</v>
+        <v>450.47</v>
       </c>
       <c r="N5" t="n">
-        <v>850.4200000000001</v>
+        <v>867.26</v>
       </c>
       <c r="O5" t="n">
-        <v>1267.21</v>
+        <v>867.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1684</v>
+        <v>1284.05</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
       </c>
       <c r="R5" t="n">
-        <v>1665.480978078051</v>
+        <v>1684</v>
       </c>
       <c r="S5" t="n">
-        <v>1569.674747974694</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1381.113554309478</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>1129.374870927043</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>897.2021192433824</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>656.4208303737385</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>462.1967561710438</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>349.7549049762899</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>379.8134315372855</v>
+        <v>33.68</v>
       </c>
       <c r="C6" t="n">
-        <v>379.8134315372855</v>
+        <v>33.68</v>
       </c>
       <c r="D6" t="n">
-        <v>379.8134315372855</v>
+        <v>33.68</v>
       </c>
       <c r="E6" t="n">
         <v>33.68</v>
@@ -4664,25 +4664,25 @@
         <v>865.523468466658</v>
       </c>
       <c r="S6" t="n">
-        <v>798.2871048660405</v>
+        <v>440.2709432141327</v>
       </c>
       <c r="T6" t="n">
-        <v>792.8752208079458</v>
+        <v>101.3132417241646</v>
       </c>
       <c r="U6" t="n">
-        <v>792.6627362016965</v>
+        <v>101.1007571179154</v>
       </c>
       <c r="V6" t="n">
-        <v>432.5769490678068</v>
+        <v>86.44351753052129</v>
       </c>
       <c r="W6" t="n">
-        <v>399.8768047144446</v>
+        <v>53.74337317715914</v>
       </c>
       <c r="X6" t="n">
-        <v>379.8134315372855</v>
+        <v>33.68</v>
       </c>
       <c r="Y6" t="n">
-        <v>379.8134315372855</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="7">
@@ -4692,25 +4692,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>756.6003030646092</v>
+        <v>740.0530652837565</v>
       </c>
       <c r="C7" t="n">
-        <v>882.602308883045</v>
+        <v>866.0550711021923</v>
       </c>
       <c r="D7" t="n">
-        <v>882.602308883045</v>
+        <v>979.3742152271924</v>
       </c>
       <c r="E7" t="n">
-        <v>1000.431213094458</v>
+        <v>1097.203119438605</v>
       </c>
       <c r="F7" t="n">
-        <v>1000.431213094458</v>
+        <v>1221.564092030541</v>
       </c>
       <c r="G7" t="n">
-        <v>1153.837778981343</v>
+        <v>1374.970657917426</v>
       </c>
       <c r="H7" t="n">
-        <v>1323.354364140741</v>
+        <v>1544.487243076824</v>
       </c>
       <c r="I7" t="n">
         <v>1544.487243076824</v>
@@ -4743,25 +4743,25 @@
         <v>33.68</v>
       </c>
       <c r="S7" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T7" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="U7" t="n">
-        <v>317.4814477324597</v>
+        <v>33.68</v>
       </c>
       <c r="V7" t="n">
-        <v>321.9212561144462</v>
+        <v>193.9647176545611</v>
       </c>
       <c r="W7" t="n">
-        <v>493.8121743741236</v>
+        <v>365.8556359142385</v>
       </c>
       <c r="X7" t="n">
-        <v>644.8429653983171</v>
+        <v>516.886426938432</v>
       </c>
       <c r="Y7" t="n">
-        <v>644.8429653983171</v>
+        <v>628.2957276174643</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>115.3301851396645</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>65.35586368209485</v>
+        <v>235.472016596655</v>
       </c>
       <c r="D8" t="n">
-        <v>54.91227202568093</v>
+        <v>225.028424940241</v>
       </c>
       <c r="E8" t="n">
-        <v>50.50490878641967</v>
+        <v>220.6210617009798</v>
       </c>
       <c r="F8" t="n">
-        <v>45.565889889438</v>
+        <v>215.6820428039981</v>
       </c>
       <c r="G8" t="n">
-        <v>41.77056434699738</v>
+        <v>211.8867172615575</v>
       </c>
       <c r="H8" t="n">
-        <v>33.68</v>
+        <v>185.2771309926108</v>
       </c>
       <c r="I8" t="n">
         <v>33.68</v>
@@ -4798,7 +4798,7 @@
         <v>424.9891130376557</v>
       </c>
       <c r="K8" t="n">
-        <v>841.7791130376557</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="L8" t="n">
         <v>841.7791130376557</v>
@@ -4807,13 +4807,13 @@
         <v>1258.569113037656</v>
       </c>
       <c r="N8" t="n">
-        <v>1258.569113037656</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="O8" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="P8" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="Q8" t="n">
         <v>1684</v>
@@ -4840,7 +4840,7 @@
         <v>480.7157780929932</v>
       </c>
       <c r="Y8" t="n">
-        <v>198.1577739836791</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>496.0291155388109</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="C9" t="n">
-        <v>496.0291155388109</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="D9" t="n">
-        <v>496.0291155388109</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="E9" t="n">
-        <v>496.0291155388109</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="F9" t="n">
-        <v>152.96220408641</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="G9" t="n">
         <v>33.68</v>
@@ -4904,22 +4904,22 @@
         <v>973.1146453614743</v>
       </c>
       <c r="T9" t="n">
-        <v>563.6623572629755</v>
+        <v>834.383479981768</v>
       </c>
       <c r="U9" t="n">
-        <v>563.4498726567263</v>
+        <v>430.1305913351147</v>
       </c>
       <c r="V9" t="n">
-        <v>548.7926330693322</v>
+        <v>415.4733517477206</v>
       </c>
       <c r="W9" t="n">
-        <v>516.09248871597</v>
+        <v>382.7732073943585</v>
       </c>
       <c r="X9" t="n">
-        <v>496.0291155388109</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="Y9" t="n">
-        <v>496.0291155388109</v>
+        <v>362.7098342171994</v>
       </c>
     </row>
     <row r="10">
@@ -4929,19 +4929,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>256.8466383453244</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="C10" t="n">
-        <v>382.8486441637601</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="D10" t="n">
-        <v>440.1997275886753</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="E10" t="n">
-        <v>558.0286318000883</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="F10" t="n">
-        <v>682.3896043920238</v>
+        <v>528.9830385051386</v>
       </c>
       <c r="G10" t="n">
         <v>682.3896043920238</v>
@@ -4980,25 +4980,25 @@
         <v>33.68</v>
       </c>
       <c r="S10" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>33.68</v>
+        <v>259.005934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>33.68</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="V10" t="n">
-        <v>33.68</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="W10" t="n">
-        <v>33.68</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="X10" t="n">
-        <v>33.68</v>
+        <v>505.5571268912646</v>
       </c>
       <c r="Y10" t="n">
-        <v>145.0893006790322</v>
+        <v>505.5571268912646</v>
       </c>
     </row>
     <row r="11">
@@ -5014,13 +5014,13 @@
         <v>332.9265620512004</v>
       </c>
       <c r="D11" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E11" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F11" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
         <v>103.3156148520479</v>
@@ -5032,25 +5032,25 @@
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="L11" t="n">
-        <v>436.0291130376557</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M11" t="n">
-        <v>946.8779417665908</v>
+        <v>1129.18</v>
       </c>
       <c r="N11" t="n">
-        <v>1500.287941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="O11" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="P11" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>275.2516144816847</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C12" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D12" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E12" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F12" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G12" t="n">
-        <v>264.0395817084329</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H12" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I12" t="n">
         <v>44.72</v>
@@ -5132,31 +5132,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>430.6159466613296</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>360.0475229791199</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>310.1572272557519</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="13">
@@ -5245,37 +5245,37 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="K14" t="n">
-        <v>436.0291130376557</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="L14" t="n">
-        <v>575.7700000000003</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M14" t="n">
         <v>575.7700000000003</v>
@@ -5296,25 +5296,25 @@
         <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>275.2516144816847</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G15" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H15" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I15" t="n">
         <v>44.72</v>
@@ -5372,28 +5372,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y15" t="n">
-        <v>310.1572272557519</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C17" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D17" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E17" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F17" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G17" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H17" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
@@ -5512,19 +5512,19 @@
         <v>44.72</v>
       </c>
       <c r="L17" t="n">
-        <v>598.13</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M17" t="n">
-        <v>1108.978828728935</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N17" t="n">
-        <v>1662.388828728935</v>
+        <v>1129.18</v>
       </c>
       <c r="O17" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5533,25 +5533,25 @@
         <v>2236</v>
       </c>
       <c r="S17" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T17" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U17" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V17" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W17" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X17" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y17" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E18" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H18" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I18" t="n">
         <v>44.72</v>
@@ -5609,28 +5609,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S18" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T18" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U18" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V18" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W18" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X18" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1192.195551353737</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C19" t="n">
-        <v>1268.697557172173</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D19" t="n">
-        <v>1332.516701297173</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E19" t="n">
-        <v>1400.845605508586</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F19" t="n">
-        <v>1475.706578100521</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G19" t="n">
-        <v>1579.613143987407</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H19" t="n">
-        <v>1699.629729146804</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I19" t="n">
-        <v>1863.55182541068</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J19" t="n">
-        <v>2175.135566063132</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K19" t="n">
-        <v>2236</v>
+        <v>1921.561060958496</v>
       </c>
       <c r="L19" t="n">
-        <v>2161.709466507294</v>
+        <v>1847.270527465789</v>
       </c>
       <c r="M19" t="n">
-        <v>1989.354303474415</v>
+        <v>1674.915364432911</v>
       </c>
       <c r="N19" t="n">
-        <v>1765.935035523218</v>
+        <v>1451.496096481714</v>
       </c>
       <c r="O19" t="n">
-        <v>1472.555677867648</v>
+        <v>1158.116738826143</v>
       </c>
       <c r="P19" t="n">
-        <v>1131.699215919893</v>
+        <v>817.2602768783884</v>
       </c>
       <c r="Q19" t="n">
-        <v>752.0635932677734</v>
+        <v>437.6246542262692</v>
       </c>
       <c r="R19" t="n">
-        <v>371.6574033878228</v>
+        <v>57.21846434631862</v>
       </c>
       <c r="S19" t="n">
-        <v>359.1589390415042</v>
+        <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>497.7346182003091</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U19" t="n">
-        <v>694.7858108385957</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V19" t="n">
-        <v>844.1072037245417</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W19" t="n">
-        <v>966.4981219842191</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X19" t="n">
-        <v>1068.028913008413</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y19" t="n">
-        <v>1129.938213687445</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="20">
@@ -5746,19 +5746,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L20" t="n">
-        <v>1542.849113037656</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M20" t="n">
-        <v>2053.697941766591</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N20" t="n">
-        <v>2236</v>
+        <v>1129.18</v>
       </c>
       <c r="O20" t="n">
-        <v>2236</v>
+        <v>1682.59</v>
       </c>
       <c r="P20" t="n">
         <v>2236</v>
@@ -5798,25 +5798,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>275.2516144816847</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C21" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D21" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E21" t="n">
-        <v>264.0395817084329</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F21" t="n">
-        <v>264.0395817084329</v>
+        <v>118.4993133207734</v>
       </c>
       <c r="G21" t="n">
-        <v>264.0395817084329</v>
+        <v>118.4993133207734</v>
       </c>
       <c r="H21" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I21" t="n">
         <v>44.72</v>
@@ -5843,31 +5843,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S21" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T21" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U21" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>430.6159466613296</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>360.0475229791199</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y21" t="n">
-        <v>310.1572272557519</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="22">
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
         <v>328.9211162073474</v>
@@ -5980,22 +5980,22 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>690.5809049473327</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M23" t="n">
-        <v>690.5809049473327</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N23" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P23" t="n">
         <v>1797.400904947332</v>
@@ -6007,25 +6007,25 @@
         <v>2236</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6038,16 +6038,16 @@
         <v>119.2429040110725</v>
       </c>
       <c r="C24" t="n">
-        <v>108.0308712378207</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D24" t="n">
-        <v>108.0308712378207</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E24" t="n">
-        <v>108.0308712378207</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F24" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G24" t="n">
         <v>44.72</v>
@@ -6089,7 +6089,7 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U24" t="n">
         <v>422.9747211415747</v>
@@ -6098,13 +6098,13 @@
         <v>357.8124310491301</v>
       </c>
       <c r="W24" t="n">
-        <v>274.6072361907175</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X24" t="n">
         <v>204.0388125085078</v>
       </c>
       <c r="Y24" t="n">
-        <v>154.1485167851398</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="25">
@@ -6168,10 +6168,10 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V25" t="n">
         <v>521.9574820108303</v>
@@ -6217,25 +6217,25 @@
         <v>53.76</v>
       </c>
       <c r="J26" t="n">
-        <v>445.0691130376557</v>
+        <v>233.3708514962949</v>
       </c>
       <c r="K26" t="n">
-        <v>445.0691130376557</v>
+        <v>898.6508514962949</v>
       </c>
       <c r="L26" t="n">
-        <v>445.0691130376557</v>
+        <v>898.6508514962949</v>
       </c>
       <c r="M26" t="n">
-        <v>955.9179417665907</v>
+        <v>1409.49968022523</v>
       </c>
       <c r="N26" t="n">
-        <v>955.9179417665907</v>
+        <v>2022.719999999993</v>
       </c>
       <c r="O26" t="n">
-        <v>1621.197941766598</v>
+        <v>2688</v>
       </c>
       <c r="P26" t="n">
-        <v>2286.477941766604</v>
+        <v>2688</v>
       </c>
       <c r="Q26" t="n">
         <v>2688</v>
@@ -6244,22 +6244,22 @@
         <v>2688</v>
       </c>
       <c r="S26" t="n">
-        <v>2509.365487068361</v>
+        <v>2514.92529374976</v>
       </c>
       <c r="T26" t="n">
-        <v>2237.976010574862</v>
+        <v>2243.535817256261</v>
       </c>
       <c r="U26" t="n">
-        <v>1903.409044364144</v>
+        <v>1908.968851045543</v>
       </c>
       <c r="V26" t="n">
-        <v>1588.408009852201</v>
+        <v>1593.9678165336</v>
       </c>
       <c r="W26" t="n">
-        <v>1264.798438154274</v>
+        <v>1270.358244835673</v>
       </c>
       <c r="X26" t="n">
-        <v>987.7460811232962</v>
+        <v>993.3058878046958</v>
       </c>
       <c r="Y26" t="n">
         <v>798.035753781659</v>
@@ -6293,7 +6293,7 @@
         <v>53.76</v>
       </c>
       <c r="I27" t="n">
-        <v>53.76</v>
+        <v>59.29119898333113</v>
       </c>
       <c r="J27" t="n">
         <v>183.2477191586301</v>
@@ -6381,25 +6381,25 @@
         <v>1431.431843630702</v>
       </c>
       <c r="L28" t="n">
-        <v>1324.818077814764</v>
+        <v>1431.431843630702</v>
       </c>
       <c r="M28" t="n">
-        <v>1324.818077814764</v>
+        <v>1431.431843630702</v>
       </c>
       <c r="N28" t="n">
-        <v>1069.075577540335</v>
+        <v>1251.627971449522</v>
       </c>
       <c r="O28" t="n">
-        <v>883.7202459158898</v>
+        <v>1251.627971449522</v>
       </c>
       <c r="P28" t="n">
-        <v>510.5405516449025</v>
+        <v>878.4482771785345</v>
       </c>
       <c r="Q28" t="n">
-        <v>98.58169666955095</v>
+        <v>466.4894222031829</v>
       </c>
       <c r="R28" t="n">
-        <v>98.58169666955095</v>
+        <v>53.76</v>
       </c>
       <c r="S28" t="n">
         <v>53.76</v>
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>632.3798821093615</v>
+        <v>626.8200754280788</v>
       </c>
       <c r="C29" t="n">
-        <v>499.577277823509</v>
+        <v>494.0174711422263</v>
       </c>
       <c r="D29" t="n">
-        <v>406.3054033388123</v>
+        <v>400.7455966575296</v>
       </c>
       <c r="E29" t="n">
-        <v>319.0697572712681</v>
+        <v>313.5099505899855</v>
       </c>
       <c r="F29" t="n">
-        <v>231.3024555460037</v>
+        <v>225.742648864721</v>
       </c>
       <c r="G29" t="n">
         <v>144.6788471752802</v>
@@ -6457,49 +6457,49 @@
         <v>445.0691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>898.6508514963019</v>
+        <v>970.9005851725746</v>
       </c>
       <c r="L29" t="n">
-        <v>1563.930851496302</v>
+        <v>970.9005851725746</v>
       </c>
       <c r="M29" t="n">
-        <v>2074.779680225237</v>
+        <v>970.9005851725746</v>
       </c>
       <c r="N29" t="n">
-        <v>2688</v>
+        <v>1584.120904947338</v>
       </c>
       <c r="O29" t="n">
-        <v>2688</v>
+        <v>1584.120904947338</v>
       </c>
       <c r="P29" t="n">
-        <v>2688</v>
+        <v>2249.400904947332</v>
       </c>
       <c r="Q29" t="n">
         <v>2688</v>
       </c>
       <c r="R29" t="n">
-        <v>2688</v>
+        <v>2688.000000000117</v>
       </c>
       <c r="S29" t="n">
-        <v>2509.365487068361</v>
+        <v>2509.365487068478</v>
       </c>
       <c r="T29" t="n">
-        <v>2237.976010574862</v>
+        <v>2237.976010574979</v>
       </c>
       <c r="U29" t="n">
-        <v>1908.968851045543</v>
+        <v>1903.409044364261</v>
       </c>
       <c r="V29" t="n">
-        <v>1593.9678165336</v>
+        <v>1588.408009852317</v>
       </c>
       <c r="W29" t="n">
-        <v>1270.358244835673</v>
+        <v>1264.798438154391</v>
       </c>
       <c r="X29" t="n">
-        <v>993.3058878046958</v>
+        <v>987.7460811234131</v>
       </c>
       <c r="Y29" t="n">
-        <v>798.035753781659</v>
+        <v>792.4759471003763</v>
       </c>
     </row>
     <row r="30">
@@ -6530,49 +6530,49 @@
         <v>53.76</v>
       </c>
       <c r="I30" t="n">
-        <v>59.29119898333113</v>
+        <v>59.29119898330475</v>
       </c>
       <c r="J30" t="n">
-        <v>183.2477191586301</v>
+        <v>183.2477191586037</v>
       </c>
       <c r="K30" t="n">
-        <v>372.4405352530135</v>
+        <v>372.4405352529871</v>
       </c>
       <c r="L30" t="n">
-        <v>643.7909968482136</v>
+        <v>643.7909968481872</v>
       </c>
       <c r="M30" t="n">
-        <v>729.8715385910729</v>
+        <v>729.8715385910465</v>
       </c>
       <c r="N30" t="n">
-        <v>863.1518231986412</v>
+        <v>863.1518231986148</v>
       </c>
       <c r="O30" t="n">
-        <v>1102.19427488236</v>
+        <v>1102.194274882334</v>
       </c>
       <c r="P30" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.72361935184</v>
       </c>
       <c r="Q30" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.72361935184</v>
       </c>
       <c r="R30" t="n">
-        <v>983.1339251171403</v>
+        <v>983.1339251171139</v>
       </c>
       <c r="S30" t="n">
-        <v>833.0692786882399</v>
+        <v>833.0692786882136</v>
       </c>
       <c r="T30" t="n">
-        <v>744.8291118018624</v>
+        <v>744.829111801836</v>
       </c>
       <c r="U30" t="n">
-        <v>661.7883443673303</v>
+        <v>661.7883443673039</v>
       </c>
       <c r="V30" t="n">
-        <v>564.3028219516534</v>
+        <v>564.302821951627</v>
       </c>
       <c r="W30" t="n">
-        <v>448.7743947700085</v>
+        <v>448.7743947699821</v>
       </c>
       <c r="X30" t="n">
         <v>345.8827387645665</v>
@@ -6621,19 +6621,19 @@
         <v>1431.431843630702</v>
       </c>
       <c r="M31" t="n">
-        <v>1226.753448274591</v>
+        <v>1431.431843630702</v>
       </c>
       <c r="N31" t="n">
-        <v>1226.753448274591</v>
+        <v>1175.689343356273</v>
       </c>
       <c r="O31" t="n">
-        <v>1226.753448274591</v>
+        <v>849.9867533774702</v>
       </c>
       <c r="P31" t="n">
-        <v>878.4482771785345</v>
+        <v>476.8070591064829</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.4894222031829</v>
+        <v>64.84820413113135</v>
       </c>
       <c r="R31" t="n">
         <v>53.76</v>
@@ -6676,13 +6676,13 @@
         <v>400.7455966575005</v>
       </c>
       <c r="E32" t="n">
-        <v>319.0697572712681</v>
+        <v>313.5099505899564</v>
       </c>
       <c r="F32" t="n">
-        <v>231.3024555460037</v>
+        <v>225.7426488646919</v>
       </c>
       <c r="G32" t="n">
-        <v>144.6788471752802</v>
+        <v>139.1190404939684</v>
       </c>
       <c r="H32" t="n">
         <v>53.76</v>
@@ -6703,10 +6703,10 @@
         <v>955.9179417665907</v>
       </c>
       <c r="N32" t="n">
-        <v>955.9179417665907</v>
+        <v>1569.138261541354</v>
       </c>
       <c r="O32" t="n">
-        <v>1621.197941766629</v>
+        <v>2234.418261541392</v>
       </c>
       <c r="P32" t="n">
         <v>2249.400904947332</v>
@@ -6767,40 +6767,40 @@
         <v>53.76</v>
       </c>
       <c r="I33" t="n">
-        <v>53.76</v>
+        <v>59.29119898330885</v>
       </c>
       <c r="J33" t="n">
-        <v>177.7165201752989</v>
+        <v>183.2477191586078</v>
       </c>
       <c r="K33" t="n">
-        <v>366.9093362696823</v>
+        <v>372.4405352529912</v>
       </c>
       <c r="L33" t="n">
-        <v>638.2597978648824</v>
+        <v>643.7909968481913</v>
       </c>
       <c r="M33" t="n">
-        <v>724.3403396077417</v>
+        <v>729.8715385910506</v>
       </c>
       <c r="N33" t="n">
-        <v>857.62062421531</v>
+        <v>863.1518231986189</v>
       </c>
       <c r="O33" t="n">
-        <v>1102.19427488236</v>
+        <v>1102.194274882338</v>
       </c>
       <c r="P33" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.723619351844</v>
       </c>
       <c r="Q33" t="n">
-        <v>1214.723619351867</v>
+        <v>1214.723619351844</v>
       </c>
       <c r="R33" t="n">
-        <v>983.1339251171403</v>
+        <v>983.133925117118</v>
       </c>
       <c r="S33" t="n">
-        <v>833.0692786882399</v>
+        <v>833.0692786882177</v>
       </c>
       <c r="T33" t="n">
-        <v>744.8291118018624</v>
+        <v>744.8291118018401</v>
       </c>
       <c r="U33" t="n">
         <v>661.7883443673303</v>
@@ -6858,16 +6858,16 @@
         <v>1324.818077814764</v>
       </c>
       <c r="M34" t="n">
-        <v>1324.818077814764</v>
+        <v>1120.139682458653</v>
       </c>
       <c r="N34" t="n">
-        <v>1069.075577540335</v>
+        <v>864.3971821842238</v>
       </c>
       <c r="O34" t="n">
-        <v>743.3729875615318</v>
+        <v>538.6945922054208</v>
       </c>
       <c r="P34" t="n">
-        <v>370.1932932905444</v>
+        <v>165.5148979344335</v>
       </c>
       <c r="Q34" t="n">
         <v>53.76</v>
@@ -6904,43 +6904,43 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="L35" t="n">
-        <v>989.4391130376558</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M35" t="n">
-        <v>1500.287941766591</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N35" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O35" t="n">
         <v>1797.400904947332</v>
@@ -6952,28 +6952,28 @@
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>398.9989442256527</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C36" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="D36" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="E36" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F36" t="n">
         <v>44.72</v>
@@ -7046,13 +7046,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W36" t="n">
-        <v>554.3632764052976</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X36" t="n">
-        <v>483.794852723088</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y36" t="n">
-        <v>433.9045569997199</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G37" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H37" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I37" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J37" t="n">
         <v>1860.696627021627</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
         <v>328.9211162073474</v>
@@ -7168,49 +7168,49 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M38" t="n">
-        <v>1500.287941766591</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N38" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O38" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7274,22 +7274,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X39" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y39" t="n">
-        <v>154.1485167851398</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="40">
@@ -7299,25 +7299,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I40" t="n">
         <v>1549.112886369176</v>
@@ -7378,49 +7378,49 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>690.5809049473327</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>690.5809049473327</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M41" t="n">
-        <v>690.5809049473327</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N41" t="n">
-        <v>690.5809049473327</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O41" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7432,22 +7432,22 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E42" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F42" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="G42" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="H42" t="n">
         <v>44.72</v>
@@ -7520,13 +7520,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>628.142589726071</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X42" t="n">
         <v>204.0388125085078</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.1485167851398</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="43">
@@ -7615,46 +7615,46 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K44" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="L44" t="n">
-        <v>989.4391130376558</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="M44" t="n">
-        <v>1500.287941766591</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="N44" t="n">
-        <v>1797.400904947332</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P44" t="n">
         <v>1797.400904947332</v>
@@ -7666,25 +7666,25 @@
         <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,16 +7694,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C45" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D45" t="n">
-        <v>110.1140157855959</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E45" t="n">
-        <v>110.1140157855959</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
         <v>44.72</v>
@@ -7967,22 +7967,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>8.72816864883265</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>552.9902962911499</v>
       </c>
       <c r="N2" t="n">
         <v>898.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409245</v>
+        <v>491.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>421.2870600406814</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
         <v>593.8226843274854</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>552.99029629115</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>491.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P5" t="n">
         <v>421.2870600406814</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>576.8125833173845</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,16 +8441,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>421</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>965.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>78.97603822292498</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>593.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,13 +8675,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121687</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8696,7 +8696,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>356.9661774925453</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,16 +8912,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121691</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>141.1524110730754</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
         <v>1036.248958069835</v>
@@ -9155,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,13 +9164,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>206.6237041381302</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,22 +9389,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>661.3924512348951</v>
+        <v>661.3924512348954</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q20" t="n">
         <v>172.8226843274854</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P23" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,10 +9860,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>216.4681087666004</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9872,16 +9872,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
         <v>742.2478695740995</v>
       </c>
       <c r="P26" t="n">
-        <v>672.2870600406879</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>578.4005209268753</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,13 +10100,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>458.1633721804507</v>
+        <v>531.1429011463827</v>
       </c>
       <c r="L29" t="n">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
@@ -10115,10 +10115,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>672.2870600406761</v>
       </c>
       <c r="Q29" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10346,13 +10346,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
         <v>742.2478695741313</v>
       </c>
       <c r="P32" t="n">
-        <v>634.8355076979574</v>
+        <v>15.4210432790047</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,22 +10571,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>370.3619737970638</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10820,7 +10820,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>777.3630622928068</v>
       </c>
       <c r="O38" t="n">
         <v>629.2478695740924</v>
@@ -10829,7 +10829,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>356.9661774925453</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
@@ -11054,19 +11054,19 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>629.2478695740924</v>
+        <v>254.3913627391524</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>559</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>777.3630622928066</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -24459,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.504208614585679</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.504208614585508</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24596,16 +24596,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>105.5476281577792</v>
       </c>
       <c r="M28" t="n">
         <v>202.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>75.17924181231612</v>
       </c>
       <c r="O28" t="n">
-        <v>138.9437857708145</v>
+        <v>322.445564079015</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -24614,10 +24614,10 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>408.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>44.37347970285543</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5.504208614469874</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>5.504208614585423</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24836,22 +24836,22 @@
         <v>105.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>202.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>253.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>322.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>24.62577794318111</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>397.624805891331</v>
       </c>
       <c r="S31" t="n">
         <v>44.37347970285543</v>
@@ -24891,7 +24891,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>5.504208614498651</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>5.504208614498665</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>202.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25085,7 +25085,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>94.570306067959</v>
+        <v>297.2019174705089</v>
       </c>
       <c r="R34" t="n">
         <v>408.6021279811511</v>
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8555709.788339345</v>
+        <v>8555709.788339343</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9486410.771881714</v>
+        <v>9486410.77188172</v>
       </c>
     </row>
     <row r="12">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11356302.16961294</v>
+        <v>11356302.16961295</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12300834.94986239</v>
+        <v>12300834.9498624</v>
       </c>
     </row>
     <row r="15">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14189900.5103613</v>
+        <v>14189900.51036131</v>
       </c>
     </row>
   </sheetData>
@@ -26290,25 +26290,25 @@
         <v>1259377.040332595</v>
       </c>
       <c r="I2" t="n">
-        <v>1259377.040332595</v>
+        <v>1259377.040332596</v>
       </c>
       <c r="J2" t="n">
         <v>1240934.644723166</v>
       </c>
       <c r="K2" t="n">
-        <v>1240934.644723166</v>
+        <v>1240934.644723175</v>
       </c>
       <c r="L2" t="n">
         <v>1240934.644723173</v>
       </c>
       <c r="M2" t="n">
-        <v>1259377.040332596</v>
+        <v>1259377.040332595</v>
       </c>
       <c r="N2" t="n">
         <v>1259377.040332595</v>
       </c>
       <c r="O2" t="n">
-        <v>1259377.040332595</v>
+        <v>1259377.040332596</v>
       </c>
       <c r="P2" t="n">
         <v>1259377.040332595</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359545</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724099</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809259</v>
+        <v>563849.7835743711</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>509242.089049618</v>
+        <v>511130.7051621594</v>
       </c>
       <c r="K4" t="n">
-        <v>507410.0945171365</v>
+        <v>509298.710629683</v>
       </c>
       <c r="L4" t="n">
-        <v>505575.4970691528</v>
+        <v>507464.1131816942</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>485605.6810900857</v>
+        <v>484043.0679966401</v>
       </c>
       <c r="C6" t="n">
-        <v>635830.1968536299</v>
+        <v>634267.5837601849</v>
       </c>
       <c r="D6" t="n">
-        <v>637865.4698516687</v>
+        <v>636302.856758224</v>
       </c>
       <c r="E6" t="n">
-        <v>324295.6371060602</v>
+        <v>322553.7872929521</v>
       </c>
       <c r="F6" t="n">
-        <v>654814.5324515639</v>
+        <v>653072.6826384565</v>
       </c>
       <c r="G6" t="n">
-        <v>656760.1089197492</v>
+        <v>655018.2591066418</v>
       </c>
       <c r="H6" t="n">
-        <v>658708.3857370511</v>
+        <v>656966.5359239433</v>
       </c>
       <c r="I6" t="n">
-        <v>660659.3823804111</v>
+        <v>658917.5325673042</v>
       </c>
       <c r="J6" t="n">
-        <v>221733.0136735475</v>
+        <v>219844.3975610064</v>
       </c>
       <c r="K6" t="n">
-        <v>665933.0082060291</v>
+        <v>664044.3920934916</v>
       </c>
       <c r="L6" t="n">
-        <v>667767.6056540202</v>
+        <v>665878.9895414786</v>
       </c>
       <c r="M6" t="n">
-        <v>634090.9657904952</v>
+        <v>632349.1159773868</v>
       </c>
       <c r="N6" t="n">
-        <v>670455.862825348</v>
+        <v>668714.0130122404</v>
       </c>
       <c r="O6" t="n">
-        <v>418023.6020830857</v>
+        <v>416281.7522699788</v>
       </c>
       <c r="P6" t="n">
-        <v>674394.204934096</v>
+        <v>672652.3551209886</v>
       </c>
     </row>
   </sheetData>
@@ -26990,7 +26990,7 @@
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27027,25 +27027,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>232.5447671255646</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27524,13 +27524,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>139.8182410159027</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27563,7 +27563,7 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>287.9308447084232</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27594,10 +27594,10 @@
         <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>330.3686599447279</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27606,7 +27606,7 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27648,19 +27648,19 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>382.0141117863587</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27673,7 +27673,7 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>400</v>
+        <v>381.6661682972702</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>232.5447671255646</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27758,7 +27758,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27800,16 +27800,16 @@
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>400</v>
+        <v>45.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>69.78964074244544</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>58.02573792896936</v>
+        <v>400</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27834,13 +27834,13 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
@@ -27849,7 +27849,7 @@
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
@@ -27879,16 +27879,16 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
         <v>210.0245665062577</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>203.6549651475157</v>
+        <v>361.0740654228435</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
@@ -27897,7 +27897,7 @@
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>381.6661682972701</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27976,7 +27976,7 @@
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -27998,10 +27998,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>207.6501538294814</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28040,10 +28040,10 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>268.0139114916045</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28065,22 +28065,22 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C10" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D10" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E10" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>298.045392951453</v>
+      </c>
+      <c r="G10" t="n">
         <v>400</v>
-      </c>
-      <c r="C10" t="n">
-        <v>400</v>
-      </c>
-      <c r="D10" t="n">
-        <v>343.4666053534496</v>
-      </c>
-      <c r="E10" t="n">
-        <v>400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>400</v>
-      </c>
-      <c r="G10" t="n">
-        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28134,7 +28134,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28150,16 +28150,16 @@
         <v>350</v>
       </c>
       <c r="D11" t="n">
+        <v>350</v>
+      </c>
+      <c r="E11" t="n">
+        <v>350</v>
+      </c>
+      <c r="F11" t="n">
+        <v>350</v>
+      </c>
+      <c r="G11" t="n">
         <v>346.0346086145855</v>
-      </c>
-      <c r="E11" t="n">
-        <v>350</v>
-      </c>
-      <c r="F11" t="n">
-        <v>350</v>
-      </c>
-      <c r="G11" t="n">
-        <v>350</v>
       </c>
       <c r="H11" t="n">
         <v>350</v>
@@ -28235,16 +28235,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>339.6362423378769</v>
+        <v>259.1265669988554</v>
       </c>
       <c r="G12" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
         <v>350</v>
@@ -28286,7 +28286,7 @@
         <v>350</v>
       </c>
       <c r="W12" t="n">
-        <v>327.5278884563857</v>
+        <v>350</v>
       </c>
       <c r="X12" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28432,7 +28432,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T14" t="n">
         <v>350</v>
@@ -28481,7 +28481,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28508,7 +28508,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S15" t="n">
         <v>350</v>
@@ -28529,7 +28529,7 @@
         <v>350</v>
       </c>
       <c r="Y15" t="n">
-        <v>154.448623365906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28669,7 +28669,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T17" t="n">
         <v>350</v>
@@ -28709,7 +28709,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>144.0848657037828</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
         <v>325.7395358750273</v>
@@ -28718,7 +28718,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28745,13 +28745,13 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
       </c>
       <c r="T18" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="U18" t="n">
         <v>350</v>
@@ -28797,7 +28797,7 @@
         <v>350</v>
       </c>
       <c r="I19" t="n">
-        <v>342.2113306341345</v>
+        <v>350</v>
       </c>
       <c r="J19" t="n">
         <v>350</v>
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28946,16 +28946,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>332.1680871864211</v>
+        <v>259.1265669988554</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>350</v>
@@ -28997,7 +28997,7 @@
         <v>350</v>
       </c>
       <c r="W21" t="n">
-        <v>327.5278884563857</v>
+        <v>350</v>
       </c>
       <c r="X21" t="n">
         <v>350</v>
@@ -29095,7 +29095,7 @@
         <v>350</v>
       </c>
       <c r="C23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="D23" t="n">
         <v>350</v>
@@ -29143,7 +29143,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T23" t="n">
         <v>350</v>
@@ -29183,10 +29183,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>276.9584798124344</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>325.7395358750273</v>
+        <v>263.0617733495849</v>
       </c>
       <c r="H24" t="n">
         <v>332.1680871864211</v>
@@ -29225,10 +29225,10 @@
         <v>350</v>
       </c>
       <c r="T24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V24" t="n">
         <v>350</v>
@@ -29304,13 +29304,13 @@
         <v>350</v>
       </c>
       <c r="T25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
       </c>
       <c r="V25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W25" t="n">
         <v>350</v>
@@ -29429,10 +29429,10 @@
         <v>318</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>222.713455571481</v>
       </c>
       <c r="J27" t="n">
-        <v>5.587069680132487</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988284125</v>
       </c>
       <c r="S29" t="n">
         <v>318</v>
@@ -29666,7 +29666,7 @@
         <v>318</v>
       </c>
       <c r="I30" t="n">
-        <v>222.713455571481</v>
+        <v>222.7134555714543</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29711,7 +29711,7 @@
         <v>318</v>
       </c>
       <c r="X30" t="n">
-        <v>318</v>
+        <v>318.0000000000262</v>
       </c>
       <c r="Y30" t="n">
         <v>318</v>
@@ -29903,7 +29903,7 @@
         <v>318</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>222.7134555714585</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29921,7 +29921,7 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>5.587069680132487</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -29939,7 +29939,7 @@
         <v>318</v>
       </c>
       <c r="U33" t="n">
-        <v>318</v>
+        <v>318.0000000000221</v>
       </c>
       <c r="V33" t="n">
         <v>318</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30131,7 +30131,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>325.7395358750273</v>
@@ -30182,10 +30182,10 @@
         <v>350</v>
       </c>
       <c r="W36" t="n">
-        <v>276.9584798124343</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30280,7 +30280,7 @@
         <v>350</v>
       </c>
       <c r="C38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="D38" t="n">
         <v>350</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30377,7 +30377,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>154.4486233659061</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30410,7 +30410,7 @@
         <v>350</v>
       </c>
       <c r="T39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>350</v>
@@ -30419,10 +30419,10 @@
         <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y39" t="n">
         <v>350</v>
@@ -30435,28 +30435,28 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>350</v>
+      </c>
+      <c r="C40" t="n">
+        <v>350</v>
+      </c>
+      <c r="D40" t="n">
+        <v>350</v>
+      </c>
+      <c r="E40" t="n">
+        <v>350</v>
+      </c>
+      <c r="F40" t="n">
+        <v>350</v>
+      </c>
+      <c r="G40" t="n">
+        <v>350</v>
+      </c>
+      <c r="H40" t="n">
+        <v>350</v>
+      </c>
+      <c r="I40" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="C40" t="n">
-        <v>350</v>
-      </c>
-      <c r="D40" t="n">
-        <v>350</v>
-      </c>
-      <c r="E40" t="n">
-        <v>350</v>
-      </c>
-      <c r="F40" t="n">
-        <v>350</v>
-      </c>
-      <c r="G40" t="n">
-        <v>350</v>
-      </c>
-      <c r="H40" t="n">
-        <v>350</v>
-      </c>
-      <c r="I40" t="n">
-        <v>350</v>
       </c>
       <c r="J40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30568,7 +30568,7 @@
         <v>350</v>
       </c>
       <c r="T41" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="U41" t="n">
         <v>350</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
@@ -30611,7 +30611,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>269.4903246609787</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>217.1263858913485</v>
@@ -30656,10 +30656,10 @@
         <v>350</v>
       </c>
       <c r="W42" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y42" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30802,7 +30802,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T44" t="n">
         <v>350</v>
@@ -30830,19 +30830,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>342.6720972219126</v>
+        <v>279.9943346964701</v>
       </c>
       <c r="F45" t="n">
-        <v>274.8961667101369</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>325.7395358750273</v>
@@ -34746,22 +34746,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K2" t="n">
-        <v>8.72816864883265</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>8.728168648832595</v>
       </c>
       <c r="N2" t="n">
         <v>421</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="P2" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>421</v>
@@ -34880,10 +34880,10 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>57.64341329668321</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,7 +34892,7 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
@@ -34934,19 +34934,19 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>134.5704663562512</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>421</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>8.728168648832652</v>
-      </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="O5" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>421</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>403.989898989899</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35120,13 +35120,13 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>154.95612715847</v>
@@ -35135,7 +35135,7 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35165,16 +35165,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>4.48465493129949</v>
+        <v>161.9037552066274</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
@@ -35183,7 +35183,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,16 +35220,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>421</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>421</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="O8" t="n">
         <v>8.728168648832536</v>
@@ -35238,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,22 +35351,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>57.93038729789409</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>23.66253698371106</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
         <v>171.2288738983814</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -35420,7 +35420,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,13 +35454,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612654</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35475,7 +35475,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35691,16 +35691,16 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612659</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>141.1524110730754</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
         <v>559</v>
@@ -35934,7 +35934,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,13 +35943,13 @@
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>136.3758345640378</v>
+        <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36083,7 +36083,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I19" t="n">
-        <v>165.5778750140162</v>
+        <v>173.3665443798817</v>
       </c>
       <c r="J19" t="n">
         <v>314.7310511640923</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36168,22 +36168,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>184.1434931650599</v>
+        <v>184.1434931650601</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P23" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36590,13 +36590,13 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W25" t="n">
         <v>123.6271901612903</v>
@@ -36639,10 +36639,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>395.2617303410664</v>
+        <v>181.4251025215101</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>672</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36651,16 +36651,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
         <v>672.000000000007</v>
       </c>
       <c r="P26" t="n">
-        <v>672.0000000000065</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>405.5778365993898</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,10 +36715,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5.587069680132455</v>
       </c>
       <c r="J27" t="n">
-        <v>130.7956759178082</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K27" t="n">
         <v>191.1038546407913</v>
@@ -36879,13 +36879,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>458.1633721804507</v>
+        <v>531.1429011463827</v>
       </c>
       <c r="L29" t="n">
-        <v>672</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
@@ -36894,13 +36894,13 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>671.9999999999947</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.180505749270922e-10</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>5.587069680132455</v>
+        <v>5.587069680105813</v>
       </c>
       <c r="J30" t="n">
         <v>125.2086062376757</v>
@@ -37125,13 +37125,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
         <v>672.0000000000389</v>
       </c>
       <c r="P32" t="n">
-        <v>634.5484476572759</v>
+        <v>15.13398323832329</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>5.587069680109947</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37207,7 +37207,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
-        <v>247.0440915828788</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
         <v>113.6660045146532</v>
@@ -37350,22 +37350,22 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>300.1141042229714</v>
+        <v>559</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37590,7 +37590,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -37599,7 +37599,7 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>300.1141042229716</v>
       </c>
       <c r="O38" t="n">
         <v>559</v>
@@ -37608,7 +37608,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>184.1434931650599</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37721,7 +37721,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C40" t="n">
         <v>77.27475335195533</v>
@@ -37742,7 +37742,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I40" t="n">
-        <v>173.3665443798817</v>
+        <v>165.577875014016</v>
       </c>
       <c r="J40" t="n">
         <v>314.7310511640923</v>
@@ -37824,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
         <v>559</v>
@@ -37833,19 +37833,19 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
+        <v>93.38475247205324</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>559</v>
       </c>
-      <c r="M44" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N44" t="n">
-        <v>300.1141042229714</v>
-      </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
